--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\2D_Evaulation\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\2DProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,93 +19,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <x:si>
-    <x:t>skill_normalSword_01</x:t>
+    <x:t>character_selly_01</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_rest_coffee_01</x:t>
+    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
   </x:si>
   <x:si>
-    <x:t>퐁당퐁당 왕국의 공주로써 백성들을 위해&lt;nl&gt;식량을 구하러 모험을 떠나는 캐릭터</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
+    <x:t>Weapon_Sword_1</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>BasicCostumeId</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
+    <x:t>skill_sword_01</x:t>
   </x:si>
   <x:si>
-    <x:t>셀리</x:t>
+    <x:t>UseWeaponId</x:t>
   </x:si>
   <x:si>
-    <x:t>다니엘</x:t>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>스킬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빅토르</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소환 마법을 사용할 수 있는 캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_daniel_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_CoffeeCup_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_victor_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_selly_01</x:t>
+    <x:t>SkillList</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잉여로운 버프 캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseWeaponId</x:t>
-  </x:si>
-  <x:si>
     <x:t>Costume_03</x:t>
   </x:si>
   <x:si>
-    <x:t>SkillList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_sword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Sword_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BasicCostumeId</x:t>
+    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -923,83 +896,83 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G2" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="G4" s="5">
         <x:v>100</x:v>
@@ -1014,21 +987,11 @@
       <x:c r="O4" s="5"/>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
+      <x:c r="A5" s="4"/>
+      <x:c r="B5" s="6"/>
+      <x:c r="C5" s="6"/>
+      <x:c r="D5" s="5"/>
+      <x:c r="E5" s="5"/>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5"/>
@@ -1041,21 +1004,11 @@
       <x:c r="O5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
+      <x:c r="A6" s="6"/>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="5"/>
+      <x:c r="E6" s="5"/>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>

--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18852" windowHeight="6744"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="18852" windowHeight="6720"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,13 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <x:si>
-    <x:t>character_selly_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 별로 무기가 고정인 경우용</x:t>
-  </x:si>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <x:si>
     <x:t>int</x:t>
   </x:si>
@@ -42,7 +36,22 @@
     <x:t>스킬</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>character_selly_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Costume_03</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
@@ -51,34 +60,16 @@
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>Weapon_Sword_1</x:t>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>BasicCostumeId</x:t>
+    <x:t>skill_sword_01</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_sword_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseWeaponId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Costume_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
+    <x:t>BasicCostumeId</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -225,7 +216,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -266,9 +257,6 @@
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -888,95 +876,83 @@
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="72" style="3" customWidth="1"/>
     <x:col min="4" max="4" width="40.22265625" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="7" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="26.54296875" style="3" customWidth="1"/>
+    <x:col min="6" max="7" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
     <x:col min="8" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
+      <x:c r="D4" s="5" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F3" s="15" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E4" s="5" t="s">
+      <x:c r="E4" s="15" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G4" s="5">
+      <x:c r="F4" s="5">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="G4" s="5"/>
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
@@ -1188,12 +1164,11 @@
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
     </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="19" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
       <x:c r="D19" s="5"/>
-      <x:c r="E19" s="5"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
@@ -1220,29 +1195,25 @@
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="9"/>
     </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A25" s="9"/>
       <x:c r="B25" s="9"/>
       <x:c r="C25" s="9"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+    </x:row>
+    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
-      <x:c r="E28" s="5"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A29" s="10"/>

--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -19,39 +19,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <x:si>
-    <x:t>int</x:t>
+    <x:t>character_selly_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
   </x:si>
   <x:si>
     <x:t>Hp</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>character_selly_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Costume_03</x:t>
+    <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
@@ -63,20 +45,29 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_sword_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
     <x:t>BasicCostumeId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Costume_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="8">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -109,11 +100,6 @@
     </x:font>
     <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
@@ -216,15 +202,12 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
@@ -253,7 +236,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -872,383 +855,370 @@
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="72" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="40.22265625" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="6" max="7" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="16384" width="12.54296875" style="3"/>
+    <x:col min="1" max="1" width="19.453125" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="72" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="26.54296875" style="2" customWidth="1"/>
+    <x:col min="5" max="7" width="12.54296875" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="16384" width="12.54296875" style="2"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+    </x:row>
+    <x:row r="2" spans="1:5" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
+    <x:row r="3" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="5">
+      <x:c r="E4" s="4">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
-      <x:c r="K4" s="5"/>
-      <x:c r="L4" s="5"/>
-      <x:c r="M4" s="5"/>
-      <x:c r="N4" s="5"/>
-      <x:c r="O4" s="5"/>
+      <x:c r="F4" s="4"/>
+      <x:c r="G4" s="4"/>
+      <x:c r="H4" s="4"/>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+      <x:c r="L4" s="4"/>
+      <x:c r="M4" s="4"/>
+      <x:c r="N4" s="4"/>
+      <x:c r="O4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4"/>
-      <x:c r="B5" s="6"/>
-      <x:c r="C5" s="6"/>
-      <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
-      <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
-      <x:c r="K5" s="5"/>
-      <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
-      <x:c r="O5" s="5"/>
+      <x:c r="A5" s="3"/>
+      <x:c r="B5" s="5"/>
+      <x:c r="C5" s="5"/>
+      <x:c r="D5" s="4"/>
+      <x:c r="E5" s="4"/>
+      <x:c r="F5" s="4"/>
+      <x:c r="G5" s="4"/>
+      <x:c r="H5" s="4"/>
+      <x:c r="I5" s="4"/>
+      <x:c r="J5" s="4"/>
+      <x:c r="K5" s="4"/>
+      <x:c r="L5" s="4"/>
+      <x:c r="M5" s="4"/>
+      <x:c r="N5" s="4"/>
+      <x:c r="O5" s="4"/>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6"/>
-      <x:c r="B6" s="6"/>
-      <x:c r="C6" s="6"/>
-      <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
-      <x:c r="G6" s="5"/>
-      <x:c r="H6" s="5"/>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5"/>
-      <x:c r="K6" s="5"/>
-      <x:c r="L6" s="5"/>
-      <x:c r="M6" s="5"/>
-      <x:c r="N6" s="5"/>
-      <x:c r="O6" s="5"/>
+      <x:c r="A6" s="5"/>
+      <x:c r="B6" s="5"/>
+      <x:c r="C6" s="5"/>
+      <x:c r="D6" s="4"/>
+      <x:c r="E6" s="4"/>
+      <x:c r="F6" s="4"/>
+      <x:c r="G6" s="4"/>
+      <x:c r="H6" s="4"/>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4"/>
+      <x:c r="L6" s="4"/>
+      <x:c r="M6" s="4"/>
+      <x:c r="N6" s="4"/>
+      <x:c r="O6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4"/>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4"/>
-      <x:c r="D7" s="5"/>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5"/>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
-      <x:c r="J7" s="5"/>
-      <x:c r="K7" s="5"/>
-      <x:c r="L7" s="5"/>
-      <x:c r="M7" s="5"/>
-      <x:c r="N7" s="5"/>
-      <x:c r="O7" s="5"/>
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="4"/>
+      <x:c r="E7" s="4"/>
+      <x:c r="F7" s="4"/>
+      <x:c r="G7" s="4"/>
+      <x:c r="H7" s="4"/>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
+      <x:c r="K7" s="4"/>
+      <x:c r="L7" s="4"/>
+      <x:c r="M7" s="4"/>
+      <x:c r="N7" s="4"/>
+      <x:c r="O7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7"/>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
-      <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
-      <x:c r="J8" s="5"/>
-      <x:c r="K8" s="5"/>
-      <x:c r="L8" s="5"/>
-      <x:c r="M8" s="5"/>
-      <x:c r="N8" s="5"/>
-      <x:c r="O8" s="5"/>
+      <x:c r="A8" s="6"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="4"/>
+      <x:c r="E8" s="4"/>
+      <x:c r="F8" s="4"/>
+      <x:c r="G8" s="4"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
+      <x:c r="L8" s="4"/>
+      <x:c r="M8" s="4"/>
+      <x:c r="N8" s="4"/>
+      <x:c r="O8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="7"/>
-      <x:c r="B9" s="7"/>
-      <x:c r="C9" s="7"/>
-      <x:c r="D9" s="5"/>
-      <x:c r="E9" s="5"/>
-      <x:c r="F9" s="5"/>
-      <x:c r="G9" s="5"/>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="5"/>
-      <x:c r="J9" s="5"/>
-      <x:c r="K9" s="5"/>
-      <x:c r="L9" s="5"/>
-      <x:c r="M9" s="5"/>
-      <x:c r="N9" s="5"/>
-      <x:c r="O9" s="5"/>
+      <x:c r="A9" s="6"/>
+      <x:c r="B9" s="6"/>
+      <x:c r="C9" s="6"/>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
+      <x:c r="F9" s="4"/>
+      <x:c r="G9" s="4"/>
+      <x:c r="H9" s="4"/>
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="4"/>
+      <x:c r="K9" s="4"/>
+      <x:c r="L9" s="4"/>
+      <x:c r="M9" s="4"/>
+      <x:c r="N9" s="4"/>
+      <x:c r="O9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
-      <x:c r="J10" s="5"/>
-      <x:c r="K10" s="5"/>
-      <x:c r="L10" s="5"/>
-      <x:c r="M10" s="5"/>
-      <x:c r="N10" s="5"/>
-      <x:c r="O10" s="5"/>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="4"/>
+      <x:c r="H10" s="4"/>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="4"/>
+      <x:c r="K10" s="4"/>
+      <x:c r="L10" s="4"/>
+      <x:c r="M10" s="4"/>
+      <x:c r="N10" s="4"/>
+      <x:c r="O10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1"/>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5"/>
-      <x:c r="H11" s="5"/>
-      <x:c r="I11" s="5"/>
-      <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-      <x:c r="L11" s="5"/>
-      <x:c r="M11" s="5"/>
-      <x:c r="N11" s="5"/>
-      <x:c r="O11" s="5"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+      <x:c r="L11" s="4"/>
+      <x:c r="M11" s="4"/>
+      <x:c r="N11" s="4"/>
+      <x:c r="O11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5"/>
-      <x:c r="H12" s="5"/>
-      <x:c r="I12" s="5"/>
-      <x:c r="J12" s="5"/>
-      <x:c r="K12" s="5"/>
-      <x:c r="L12" s="5"/>
-      <x:c r="M12" s="5"/>
-      <x:c r="N12" s="5"/>
-      <x:c r="O12" s="5"/>
+      <x:c r="A12" s="6"/>
+      <x:c r="B12" s="6"/>
+      <x:c r="C12" s="6"/>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+      <x:c r="L12" s="4"/>
+      <x:c r="M12" s="4"/>
+      <x:c r="N12" s="4"/>
+      <x:c r="O12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
-      <x:c r="I13" s="5"/>
-      <x:c r="J13" s="5"/>
-      <x:c r="K13" s="5"/>
-      <x:c r="L13" s="5"/>
-      <x:c r="M13" s="5"/>
-      <x:c r="N13" s="5"/>
-      <x:c r="O13" s="5"/>
+      <x:c r="A13" s="3"/>
+      <x:c r="B13" s="3"/>
+      <x:c r="C13" s="3"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+      <x:c r="L13" s="4"/>
+      <x:c r="M13" s="4"/>
+      <x:c r="N13" s="4"/>
+      <x:c r="O13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
-      <x:c r="H14" s="5"/>
-      <x:c r="I14" s="5"/>
-      <x:c r="J14" s="5"/>
-      <x:c r="K14" s="5"/>
-      <x:c r="L14" s="5"/>
-      <x:c r="M14" s="5"/>
-      <x:c r="N14" s="5"/>
-      <x:c r="O14" s="5"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+      <x:c r="L14" s="4"/>
+      <x:c r="M14" s="4"/>
+      <x:c r="N14" s="4"/>
+      <x:c r="O14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="5"/>
-      <x:c r="H15" s="5"/>
-      <x:c r="I15" s="5"/>
-      <x:c r="J15" s="5"/>
-      <x:c r="K15" s="5"/>
-      <x:c r="L15" s="5"/>
-      <x:c r="M15" s="5"/>
-      <x:c r="N15" s="5"/>
-      <x:c r="O15" s="5"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+      <x:c r="L15" s="4"/>
+      <x:c r="M15" s="4"/>
+      <x:c r="N15" s="4"/>
+      <x:c r="O15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="8"/>
-      <x:c r="B16" s="8"/>
-      <x:c r="C16" s="8"/>
+      <x:c r="A16" s="7"/>
+      <x:c r="B16" s="7"/>
+      <x:c r="C16" s="7"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="9"/>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
+      <x:c r="A17" s="8"/>
+      <x:c r="B17" s="8"/>
+      <x:c r="C17" s="8"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="9"/>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-    </x:row>
-    <x:row r="19" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A19" s="9"/>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="5"/>
+      <x:c r="A18" s="8"/>
+      <x:c r="B18" s="8"/>
+      <x:c r="C18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A19" s="8"/>
+      <x:c r="B19" s="8"/>
+      <x:c r="C19" s="8"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="9"/>
-      <x:c r="B20" s="9"/>
-      <x:c r="C20" s="9"/>
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="8"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="9"/>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
+      <x:c r="A21" s="8"/>
+      <x:c r="B21" s="8"/>
+      <x:c r="C21" s="8"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="9"/>
-      <x:c r="B22" s="9"/>
-      <x:c r="C22" s="9"/>
+      <x:c r="A22" s="8"/>
+      <x:c r="B22" s="8"/>
+      <x:c r="C22" s="8"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="9"/>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
+      <x:c r="A23" s="8"/>
+      <x:c r="B23" s="8"/>
+      <x:c r="C23" s="8"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="9"/>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
+      <x:c r="A24" s="8"/>
+      <x:c r="B24" s="8"/>
+      <x:c r="C24" s="8"/>
     </x:row>
     <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="9"/>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
+      <x:c r="A25" s="8"/>
+      <x:c r="B25" s="8"/>
+      <x:c r="C25" s="8"/>
     </x:row>
     <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="10"/>
-      <x:c r="B26" s="10"/>
-      <x:c r="C26" s="10"/>
+      <x:c r="A26" s="9"/>
+      <x:c r="B26" s="9"/>
+      <x:c r="C26" s="9"/>
     </x:row>
     <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="10"/>
-      <x:c r="B27" s="10"/>
-      <x:c r="C27" s="10"/>
+      <x:c r="A27" s="9"/>
+      <x:c r="B27" s="9"/>
+      <x:c r="C27" s="9"/>
     </x:row>
     <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="10"/>
-      <x:c r="B28" s="10"/>
-      <x:c r="C28" s="10"/>
+      <x:c r="A28" s="9"/>
+      <x:c r="B28" s="9"/>
+      <x:c r="C28" s="9"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="10"/>
-      <x:c r="B29" s="10"/>
-      <x:c r="C29" s="10"/>
+      <x:c r="A29" s="9"/>
+      <x:c r="B29" s="9"/>
+      <x:c r="C29" s="9"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="10"/>
-      <x:c r="B30" s="10"/>
-      <x:c r="C30" s="10"/>
+      <x:c r="A30" s="9"/>
+      <x:c r="B30" s="9"/>
+      <x:c r="C30" s="9"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="10"/>
-      <x:c r="B31" s="10"/>
-      <x:c r="C31" s="10"/>
+      <x:c r="A31" s="9"/>
+      <x:c r="B31" s="9"/>
+      <x:c r="C31" s="9"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
+      <x:c r="A32" s="10"/>
+      <x:c r="B32" s="10"/>
+      <x:c r="C32" s="10"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
+      <x:c r="A33" s="10"/>
+      <x:c r="B33" s="10"/>
+      <x:c r="C33" s="10"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
+      <x:c r="A34" s="10"/>
+      <x:c r="B34" s="10"/>
+      <x:c r="C34" s="10"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
+      <x:c r="A35" s="10"/>
+      <x:c r="B35" s="10"/>
+      <x:c r="C35" s="10"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -19,15 +19,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <x:si>
-    <x:t>character_selly_01</x:t>
+    <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>토토</x:t>
+    <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>Character_Toto_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
   </x:si>
   <x:si>
     <x:t>Hp</x:t>
@@ -36,31 +39,22 @@
     <x:t>int</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토토</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BasicCostumeId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Costume_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웰빙리아국의 왕자 루이를 구하기 위해&lt;nl&gt;위험한 모험에 나선 여전사.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -153,7 +147,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="2">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -182,27 +176,13 @@
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="ff000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="ff000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="ff000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="ff000000"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -241,12 +221,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -858,70 +832,61 @@
     <x:col min="1" max="1" width="19.453125" style="2" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="72" style="2" customWidth="1"/>
-    <x:col min="4" max="4" width="26.54296875" style="2" customWidth="1"/>
-    <x:col min="5" max="7" width="12.54296875" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="7" width="12.54296875" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="16384" width="12.54296875" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:4" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
+      <x:c r="C3" s="11" t="s">
+        <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="D3" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="13" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
+      <x:c r="C4" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E4" s="4">
+      <x:c r="D4" s="4">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="E4" s="4"/>
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
